--- a/plantillas/UT_Avance.xlsx
+++ b/plantillas/UT_Avance.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Visual Studio Code\NodeJS\SIVACC\plantillas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50C5011F-4683-4248-9658-ABC5DF138C46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A99B627-BEA0-43DD-A354-5AE345B8757E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -59,7 +59,8 @@
     <t>% de Avance</t>
   </si>
   <si>
-    <t>SISTEMA DE CÓMPUTO Y VALIDACIONES PARA LAS CONSULTAS CIUDADANAS (SICOVACC)</t>
+    <t>SISTEMA DE CÓMPUTO Y VALIDACIONES PARA LAS CONSULTAS CIUDADANAS
+SICOVACC 2026</t>
   </si>
 </sst>
 </file>
@@ -187,9 +188,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -198,6 +196,9 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -538,7 +539,7 @@
       <c r="G2" s="12"/>
       <c r="H2" s="12"/>
     </row>
-    <row r="3" spans="1:8" ht="18" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="13" t="s">
         <v>9</v>
       </c>
@@ -606,14 +607,14 @@
     <row r="9" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C9" s="3"/>
       <c r="D9" s="4"/>
-      <c r="F9" s="8" t="s">
+      <c r="F9" s="11" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C10" s="3"/>
       <c r="D10" s="5"/>
-      <c r="F10" s="8" t="s">
+      <c r="F10" s="11" t="s">
         <v>4</v>
       </c>
     </row>
@@ -621,16 +622,16 @@
       <c r="E11" s="1"/>
     </row>
     <row r="12" spans="1:8" ht="52.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C12" s="9" t="s">
+      <c r="C12" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="D12" s="10" t="s">
+      <c r="D12" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="E12" s="10" t="s">
+      <c r="E12" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="F12" s="11" t="s">
+      <c r="F12" s="10" t="s">
         <v>8</v>
       </c>
     </row>

--- a/plantillas/UT_Avance.xlsx
+++ b/plantillas/UT_Avance.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Visual Studio Code\NodeJS\SIVACC\plantillas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A99B627-BEA0-43DD-A354-5AE345B8757E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECD41F0C-7C7C-4ACC-A5F0-EC54629F83D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -60,7 +60,7 @@
   </si>
   <si>
     <t>SISTEMA DE CÓMPUTO Y VALIDACIONES PARA LAS CONSULTAS CIUDADANAS
-SICOVACC 2026</t>
+SICOVACC</t>
   </si>
 </sst>
 </file>
